--- a/ZonasEscolares/excels/MADRE_DE_DIOS-TAMBOPATA-TAMBOPATA.xlsx
+++ b/ZonasEscolares/excels/MADRE_DE_DIOS-TAMBOPATA-TAMBOPATA.xlsx
@@ -486,7 +486,7 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>mantenimiento</t>
+          <t>Intervenido PI2024</t>
         </is>
       </c>
     </row>
@@ -498,7 +498,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>MADRE_DE_DIOS</t>
+          <t>MADRE DE DIOS</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -538,7 +538,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -550,7 +550,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>MADRE_DE_DIOS</t>
+          <t>MADRE DE DIOS</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -590,7 +590,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -602,7 +602,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>MADRE_DE_DIOS</t>
+          <t>MADRE DE DIOS</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -642,7 +642,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -654,7 +654,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>MADRE_DE_DIOS</t>
+          <t>MADRE DE DIOS</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -694,7 +694,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -706,7 +706,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>MADRE_DE_DIOS</t>
+          <t>MADRE DE DIOS</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -758,7 +758,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>MADRE_DE_DIOS</t>
+          <t>MADRE DE DIOS</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -798,7 +798,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -810,7 +810,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>MADRE_DE_DIOS</t>
+          <t>MADRE DE DIOS</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -850,7 +850,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -862,7 +862,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>MADRE_DE_DIOS</t>
+          <t>MADRE DE DIOS</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -902,7 +902,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -914,7 +914,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>MADRE_DE_DIOS</t>
+          <t>MADRE DE DIOS</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -954,7 +954,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -966,7 +966,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>MADRE_DE_DIOS</t>
+          <t>MADRE DE DIOS</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1006,7 +1006,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1018,7 +1018,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>MADRE_DE_DIOS</t>
+          <t>MADRE DE DIOS</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1058,7 +1058,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1070,7 +1070,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>MADRE_DE_DIOS</t>
+          <t>MADRE DE DIOS</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1110,7 +1110,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1122,7 +1122,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>MADRE_DE_DIOS</t>
+          <t>MADRE DE DIOS</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1174,7 +1174,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>MADRE_DE_DIOS</t>
+          <t>MADRE DE DIOS</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1214,7 +1214,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1226,7 +1226,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>MADRE_DE_DIOS</t>
+          <t>MADRE DE DIOS</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1278,7 +1278,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>MADRE_DE_DIOS</t>
+          <t>MADRE DE DIOS</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1318,7 +1318,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1330,7 +1330,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>MADRE_DE_DIOS</t>
+          <t>MADRE DE DIOS</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1370,7 +1370,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1382,7 +1382,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>MADRE_DE_DIOS</t>
+          <t>MADRE DE DIOS</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1422,7 +1422,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1434,7 +1434,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>MADRE_DE_DIOS</t>
+          <t>MADRE DE DIOS</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1474,7 +1474,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1486,7 +1486,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>MADRE_DE_DIOS</t>
+          <t>MADRE DE DIOS</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1526,7 +1526,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1538,7 +1538,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>MADRE_DE_DIOS</t>
+          <t>MADRE DE DIOS</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1578,7 +1578,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1590,7 +1590,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>MADRE_DE_DIOS</t>
+          <t>MADRE DE DIOS</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1630,7 +1630,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1642,7 +1642,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>MADRE_DE_DIOS</t>
+          <t>MADRE DE DIOS</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1682,7 +1682,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>MADRE_DE_DIOS</t>
+          <t>MADRE DE DIOS</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1734,7 +1734,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1746,7 +1746,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>MADRE_DE_DIOS</t>
+          <t>MADRE DE DIOS</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1786,7 +1786,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1798,7 +1798,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>MADRE_DE_DIOS</t>
+          <t>MADRE DE DIOS</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1838,7 +1838,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1850,7 +1850,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>MADRE_DE_DIOS</t>
+          <t>MADRE DE DIOS</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1890,7 +1890,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1902,7 +1902,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>MADRE_DE_DIOS</t>
+          <t>MADRE DE DIOS</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1942,7 +1942,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1954,7 +1954,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>MADRE_DE_DIOS</t>
+          <t>MADRE DE DIOS</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1994,7 +1994,7 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -2006,7 +2006,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>MADRE_DE_DIOS</t>
+          <t>MADRE DE DIOS</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2046,7 +2046,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2058,7 +2058,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>MADRE_DE_DIOS</t>
+          <t>MADRE DE DIOS</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2098,7 +2098,7 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2110,7 +2110,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>MADRE_DE_DIOS</t>
+          <t>MADRE DE DIOS</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2150,7 +2150,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2162,7 +2162,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>MADRE_DE_DIOS</t>
+          <t>MADRE DE DIOS</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2202,7 +2202,7 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -2214,7 +2214,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>MADRE_DE_DIOS</t>
+          <t>MADRE DE DIOS</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2254,7 +2254,7 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2266,7 +2266,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>MADRE_DE_DIOS</t>
+          <t>MADRE DE DIOS</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2318,7 +2318,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>MADRE_DE_DIOS</t>
+          <t>MADRE DE DIOS</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2358,7 +2358,7 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -2370,7 +2370,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>MADRE_DE_DIOS</t>
+          <t>MADRE DE DIOS</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2410,7 +2410,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2422,7 +2422,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>MADRE_DE_DIOS</t>
+          <t>MADRE DE DIOS</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2462,7 +2462,7 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2474,7 +2474,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>MADRE_DE_DIOS</t>
+          <t>MADRE DE DIOS</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2514,7 +2514,7 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2526,7 +2526,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>MADRE_DE_DIOS</t>
+          <t>MADRE DE DIOS</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2566,7 +2566,7 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>

--- a/ZonasEscolares/excels/MADRE_DE_DIOS-TAMBOPATA-TAMBOPATA.xlsx
+++ b/ZonasEscolares/excels/MADRE_DE_DIOS-TAMBOPATA-TAMBOPATA.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,62 +417,62 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>ubigeo_gestor</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>departamento</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>provincia</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>distrito</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>codigo_ce</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>descripcion</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>latitud</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>longitud</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>alumnos</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>docentes</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>siniestros</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Intervenido PI2024</t>
         </is>
@@ -521,20 +509,30 @@
           <t>261 NUESTRA SEÑORA DE LA ESPERANZA</t>
         </is>
       </c>
-      <c r="G2" t="n">
-        <v>-12.5839</v>
-      </c>
-      <c r="H2" t="n">
-        <v>-69.19143</v>
-      </c>
-      <c r="I2" t="n">
-        <v>342</v>
-      </c>
-      <c r="J2" t="n">
-        <v>13</v>
-      </c>
-      <c r="K2" t="n">
-        <v>1</v>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>-12.5839</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>-69.19143</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>342</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
@@ -573,20 +571,30 @@
           <t>267 CORAZON DE MARIA</t>
         </is>
       </c>
-      <c r="G3" t="n">
-        <v>-12.5921</v>
-      </c>
-      <c r="H3" t="n">
-        <v>-69.1972</v>
-      </c>
-      <c r="I3" t="n">
-        <v>200</v>
-      </c>
-      <c r="J3" t="n">
-        <v>9</v>
-      </c>
-      <c r="K3" t="n">
-        <v>0</v>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>-12.5921</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>-69.1972</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
@@ -625,20 +633,30 @@
           <t>52020 CAP. FAP JOSE ABELARDO QUIÑONES</t>
         </is>
       </c>
-      <c r="G4" t="n">
-        <v>-12.602946</v>
-      </c>
-      <c r="H4" t="n">
-        <v>-69.212059</v>
-      </c>
-      <c r="I4" t="n">
-        <v>1147</v>
-      </c>
-      <c r="J4" t="n">
-        <v>53</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0</v>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>-12.602946</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>-69.212059</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1147</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
@@ -677,20 +695,30 @@
           <t>295 ARCO IRIS</t>
         </is>
       </c>
-      <c r="G5" t="n">
-        <v>-12.6031</v>
-      </c>
-      <c r="H5" t="n">
-        <v>-69.18300000000001</v>
-      </c>
-      <c r="I5" t="n">
-        <v>262</v>
-      </c>
-      <c r="J5" t="n">
-        <v>9</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0</v>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>-12.6031</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>-69.183</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>262</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
@@ -729,20 +757,30 @@
           <t>296 LAS PALMERAS</t>
         </is>
       </c>
-      <c r="G6" t="n">
-        <v>-12.59045</v>
-      </c>
-      <c r="H6" t="n">
-        <v>-69.19264</v>
-      </c>
-      <c r="I6" t="n">
-        <v>311</v>
-      </c>
-      <c r="J6" t="n">
-        <v>12</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0</v>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>-12.59045</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>-69.19264</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>311</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
@@ -781,20 +819,30 @@
           <t>297</t>
         </is>
       </c>
-      <c r="G7" t="n">
-        <v>-12.59538</v>
-      </c>
-      <c r="H7" t="n">
-        <v>-69.18209</v>
-      </c>
-      <c r="I7" t="n">
-        <v>587</v>
-      </c>
-      <c r="J7" t="n">
-        <v>22</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>-12.59538</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>-69.18209</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>587</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
@@ -833,20 +881,30 @@
           <t>310 RAYITOS DEL SOL</t>
         </is>
       </c>
-      <c r="G8" t="n">
-        <v>-12.593892</v>
-      </c>
-      <c r="H8" t="n">
-        <v>-69.197019</v>
-      </c>
-      <c r="I8" t="n">
-        <v>250</v>
-      </c>
-      <c r="J8" t="n">
-        <v>10</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>-12.593892</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>-69.197019</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>250</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
@@ -885,20 +943,30 @@
           <t>315 HUERTO INFANTIL</t>
         </is>
       </c>
-      <c r="G9" t="n">
-        <v>-12.594395</v>
-      </c>
-      <c r="H9" t="n">
-        <v>-69.19243899999999</v>
-      </c>
-      <c r="I9" t="n">
-        <v>465</v>
-      </c>
-      <c r="J9" t="n">
-        <v>16</v>
-      </c>
-      <c r="K9" t="n">
-        <v>1</v>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>-12.594395</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>-69.192439</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>465</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
@@ -937,20 +1005,30 @@
           <t>318 MI PEQUEÑO MUNDO</t>
         </is>
       </c>
-      <c r="G10" t="n">
-        <v>-12.6015</v>
-      </c>
-      <c r="H10" t="n">
-        <v>-69.191</v>
-      </c>
-      <c r="I10" t="n">
-        <v>217</v>
-      </c>
-      <c r="J10" t="n">
-        <v>8</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>-12.6015</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>-69.191</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>217</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
@@ -989,20 +1067,30 @@
           <t>52001 SANTA ROSA</t>
         </is>
       </c>
-      <c r="G11" t="n">
-        <v>-12.587535</v>
-      </c>
-      <c r="H11" t="n">
-        <v>-69.20277900000001</v>
-      </c>
-      <c r="I11" t="n">
-        <v>832</v>
-      </c>
-      <c r="J11" t="n">
-        <v>45</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>-12.587535</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>-69.202779</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>832</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
@@ -1041,20 +1129,30 @@
           <t>NUESTRA SEÑORA DE LAS MERCEDES</t>
         </is>
       </c>
-      <c r="G12" t="n">
-        <v>-12.592886</v>
-      </c>
-      <c r="H12" t="n">
-        <v>-69.17986500000001</v>
-      </c>
-      <c r="I12" t="n">
-        <v>1555</v>
-      </c>
-      <c r="J12" t="n">
-        <v>63</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>-12.592886</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>-69.179865</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1555</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
@@ -1093,20 +1191,30 @@
           <t>52008 SANTA CRUZ</t>
         </is>
       </c>
-      <c r="G13" t="n">
-        <v>-12.59631</v>
-      </c>
-      <c r="H13" t="n">
-        <v>-69.18765</v>
-      </c>
-      <c r="I13" t="n">
-        <v>814</v>
-      </c>
-      <c r="J13" t="n">
-        <v>39</v>
-      </c>
-      <c r="K13" t="n">
-        <v>2</v>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>-12.59631</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>-69.18765</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>814</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
@@ -1145,20 +1253,30 @@
           <t>LA PASTORA</t>
         </is>
       </c>
-      <c r="G14" t="n">
-        <v>-12.585947</v>
-      </c>
-      <c r="H14" t="n">
-        <v>-69.21302</v>
-      </c>
-      <c r="I14" t="n">
-        <v>1325</v>
-      </c>
-      <c r="J14" t="n">
-        <v>60</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0</v>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>-12.585947</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>-69.21302</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1325</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
@@ -1197,20 +1315,30 @@
           <t>DOS DE MAYO</t>
         </is>
       </c>
-      <c r="G15" t="n">
-        <v>-12.58447</v>
-      </c>
-      <c r="H15" t="n">
-        <v>-69.19069</v>
-      </c>
-      <c r="I15" t="n">
-        <v>2398</v>
-      </c>
-      <c r="J15" t="n">
-        <v>92</v>
-      </c>
-      <c r="K15" t="n">
-        <v>1</v>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>-12.58447</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>-69.19069</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>2398</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>92</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
@@ -1249,20 +1377,30 @@
           <t>52166 NUESTRA SEÑORA DE FATIMA</t>
         </is>
       </c>
-      <c r="G16" t="n">
-        <v>-12.6056</v>
-      </c>
-      <c r="H16" t="n">
-        <v>-69.18989999999999</v>
-      </c>
-      <c r="I16" t="n">
-        <v>431</v>
-      </c>
-      <c r="J16" t="n">
-        <v>17</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>-12.6056</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>-69.1899</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>431</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
@@ -1301,20 +1439,30 @@
           <t>52183</t>
         </is>
       </c>
-      <c r="G17" t="n">
-        <v>-12.55695</v>
-      </c>
-      <c r="H17" t="n">
-        <v>-69.20533</v>
-      </c>
-      <c r="I17" t="n">
-        <v>461</v>
-      </c>
-      <c r="J17" t="n">
-        <v>21</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>-12.55695</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>-69.20533</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>461</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
@@ -1353,20 +1501,30 @@
           <t>52194 CAPITAN ALIPIO PONCE VASQUEZ</t>
         </is>
       </c>
-      <c r="G18" t="n">
-        <v>-12.60278</v>
-      </c>
-      <c r="H18" t="n">
-        <v>-69.19305</v>
-      </c>
-      <c r="I18" t="n">
-        <v>652</v>
-      </c>
-      <c r="J18" t="n">
-        <v>20</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0</v>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>-12.60278</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>-69.19305</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>652</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
@@ -1405,20 +1563,30 @@
           <t>FAUSTINO MALDONADO</t>
         </is>
       </c>
-      <c r="G19" t="n">
-        <v>-12.59756</v>
-      </c>
-      <c r="H19" t="n">
-        <v>-69.17791</v>
-      </c>
-      <c r="I19" t="n">
-        <v>1656</v>
-      </c>
-      <c r="J19" t="n">
-        <v>64</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0</v>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>-12.59756</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>-69.17791</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1656</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
@@ -1457,20 +1625,30 @@
           <t>AUGUSTO BOURONCLE ACUÑA</t>
         </is>
       </c>
-      <c r="G20" t="n">
-        <v>-12.5997</v>
-      </c>
-      <c r="H20" t="n">
-        <v>-69.18380000000001</v>
-      </c>
-      <c r="I20" t="n">
-        <v>1861</v>
-      </c>
-      <c r="J20" t="n">
-        <v>67</v>
-      </c>
-      <c r="K20" t="n">
-        <v>0</v>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>-12.5997</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>-69.1838</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1861</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
@@ -1509,20 +1687,30 @@
           <t>CARLOS FERMIN FITZCARRALD / COAR MADRE DE DIOS</t>
         </is>
       </c>
-      <c r="G21" t="n">
-        <v>-12.591576</v>
-      </c>
-      <c r="H21" t="n">
-        <v>-69.188401</v>
-      </c>
-      <c r="I21" t="n">
-        <v>2784</v>
-      </c>
-      <c r="J21" t="n">
-        <v>130</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0</v>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>-12.591576</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>-69.188401</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>2784</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>130</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
@@ -1561,20 +1749,30 @@
           <t>APLICACION NUESTRA SEÑORA DEL ROSARIO</t>
         </is>
       </c>
-      <c r="G22" t="n">
-        <v>-12.59046</v>
-      </c>
-      <c r="H22" t="n">
-        <v>-69.19501</v>
-      </c>
-      <c r="I22" t="n">
-        <v>1346</v>
-      </c>
-      <c r="J22" t="n">
-        <v>56</v>
-      </c>
-      <c r="K22" t="n">
-        <v>0</v>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>-12.59046</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>-69.19501</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>1346</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
@@ -1613,20 +1811,30 @@
           <t>EMBLEMATICO GUILLERMO BILLINGHURST</t>
         </is>
       </c>
-      <c r="G23" t="n">
-        <v>-12.6005</v>
-      </c>
-      <c r="H23" t="n">
-        <v>-69.18259999999999</v>
-      </c>
-      <c r="I23" t="n">
-        <v>1294</v>
-      </c>
-      <c r="J23" t="n">
-        <v>65</v>
-      </c>
-      <c r="K23" t="n">
-        <v>0</v>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>-12.6005</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>-69.1826</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>1294</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
@@ -1665,20 +1873,30 @@
           <t>JAIME WHITE</t>
         </is>
       </c>
-      <c r="G24" t="n">
-        <v>-12.59808</v>
-      </c>
-      <c r="H24" t="n">
-        <v>-69.18971000000001</v>
-      </c>
-      <c r="I24" t="n">
-        <v>885</v>
-      </c>
-      <c r="J24" t="n">
-        <v>42</v>
-      </c>
-      <c r="K24" t="n">
-        <v>0</v>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>-12.59808</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>-69.18971</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>885</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
@@ -1717,20 +1935,30 @@
           <t>SAN ISIDRO</t>
         </is>
       </c>
-      <c r="G25" t="n">
-        <v>-12.592248</v>
-      </c>
-      <c r="H25" t="n">
-        <v>-69.186452</v>
-      </c>
-      <c r="I25" t="n">
-        <v>260</v>
-      </c>
-      <c r="J25" t="n">
-        <v>26</v>
-      </c>
-      <c r="K25" t="n">
-        <v>0</v>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>-12.592248</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>-69.186452</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>260</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
@@ -1769,20 +1997,30 @@
           <t>SANTA RITA DE CASIA</t>
         </is>
       </c>
-      <c r="G26" t="n">
-        <v>-12.58893</v>
-      </c>
-      <c r="H26" t="n">
-        <v>-69.19839</v>
-      </c>
-      <c r="I26" t="n">
-        <v>215</v>
-      </c>
-      <c r="J26" t="n">
-        <v>10</v>
-      </c>
-      <c r="K26" t="n">
-        <v>0</v>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>-12.58893</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>-69.19839</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>215</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
@@ -1821,20 +2059,30 @@
           <t>52072 MARIO VARGAS LLOSA</t>
         </is>
       </c>
-      <c r="G27" t="n">
-        <v>-13.0761</v>
-      </c>
-      <c r="H27" t="n">
-        <v>-70.3591</v>
-      </c>
-      <c r="I27" t="n">
-        <v>552</v>
-      </c>
-      <c r="J27" t="n">
-        <v>25</v>
-      </c>
-      <c r="K27" t="n">
-        <v>0</v>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>-13.0761</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>-70.3591</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>552</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
@@ -1873,20 +2121,30 @@
           <t>JORGE CHAVEZ RENGIFO</t>
         </is>
       </c>
-      <c r="G28" t="n">
-        <v>-12.279092</v>
-      </c>
-      <c r="H28" t="n">
-        <v>-69.14887899999999</v>
-      </c>
-      <c r="I28" t="n">
-        <v>447</v>
-      </c>
-      <c r="J28" t="n">
-        <v>30</v>
-      </c>
-      <c r="K28" t="n">
-        <v>0</v>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>-12.279092</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>-69.148879</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>447</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
@@ -1925,20 +2183,30 @@
           <t>361 SEÑOR DE LOS MILAGROS / 52181 SEÑOR DE LOS MILAGROS / SEÑOR DE LOS MILAGROS</t>
         </is>
       </c>
-      <c r="G29" t="n">
-        <v>-12.59528</v>
-      </c>
-      <c r="H29" t="n">
-        <v>-69.20014</v>
-      </c>
-      <c r="I29" t="n">
-        <v>2030</v>
-      </c>
-      <c r="J29" t="n">
-        <v>82</v>
-      </c>
-      <c r="K29" t="n">
-        <v>0</v>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>-12.59528</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>-69.20014</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>2030</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
@@ -1977,20 +2245,30 @@
           <t>CAP. ALIPIO PONCE VASQUEZ</t>
         </is>
       </c>
-      <c r="G30" t="n">
-        <v>-12.601875</v>
-      </c>
-      <c r="H30" t="n">
-        <v>-69.196872</v>
-      </c>
-      <c r="I30" t="n">
-        <v>473</v>
-      </c>
-      <c r="J30" t="n">
-        <v>18</v>
-      </c>
-      <c r="K30" t="n">
-        <v>0</v>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>-12.601875</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>-69.196872</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>473</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
@@ -2029,20 +2307,30 @@
           <t>MARIA MOLINARI REATEGUI</t>
         </is>
       </c>
-      <c r="G31" t="n">
-        <v>-12.58061</v>
-      </c>
-      <c r="H31" t="n">
-        <v>-69.1931</v>
-      </c>
-      <c r="I31" t="n">
-        <v>324</v>
-      </c>
-      <c r="J31" t="n">
-        <v>15</v>
-      </c>
-      <c r="K31" t="n">
-        <v>0</v>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>-12.58061</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>-69.1931</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>324</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
@@ -2081,20 +2369,30 @@
           <t>SANTA FE</t>
         </is>
       </c>
-      <c r="G32" t="n">
-        <v>-12.60276</v>
-      </c>
-      <c r="H32" t="n">
-        <v>-69.19073</v>
-      </c>
-      <c r="I32" t="n">
-        <v>444</v>
-      </c>
-      <c r="J32" t="n">
-        <v>24</v>
-      </c>
-      <c r="K32" t="n">
-        <v>0</v>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>-12.60276</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>-69.19073</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>444</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
@@ -2133,20 +2431,30 @@
           <t>TRILCE</t>
         </is>
       </c>
-      <c r="G33" t="n">
-        <v>-12.59366</v>
-      </c>
-      <c r="H33" t="n">
-        <v>-69.19552</v>
-      </c>
-      <c r="I33" t="n">
-        <v>313</v>
-      </c>
-      <c r="J33" t="n">
-        <v>17</v>
-      </c>
-      <c r="K33" t="n">
-        <v>0</v>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>-12.59366</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>-69.19552</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>313</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
@@ -2185,20 +2493,30 @@
           <t>NUESTRA SEÑORA DE LA MERCED</t>
         </is>
       </c>
-      <c r="G34" t="n">
-        <v>-12.58876</v>
-      </c>
-      <c r="H34" t="n">
-        <v>-69.19971</v>
-      </c>
-      <c r="I34" t="n">
-        <v>304</v>
-      </c>
-      <c r="J34" t="n">
-        <v>20</v>
-      </c>
-      <c r="K34" t="n">
-        <v>0</v>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>-12.58876</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>-69.19971</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>304</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
@@ -2237,20 +2555,30 @@
           <t>269 JARDIN DE DIOS</t>
         </is>
       </c>
-      <c r="G35" t="n">
-        <v>-12.601576</v>
-      </c>
-      <c r="H35" t="n">
-        <v>-69.21279699999999</v>
-      </c>
-      <c r="I35" t="n">
-        <v>348</v>
-      </c>
-      <c r="J35" t="n">
-        <v>15</v>
-      </c>
-      <c r="K35" t="n">
-        <v>0</v>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>-12.601576</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>-69.212797</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>348</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
@@ -2289,20 +2617,30 @@
           <t>MARIA REINA</t>
         </is>
       </c>
-      <c r="G36" t="n">
-        <v>-12.597001</v>
-      </c>
-      <c r="H36" t="n">
-        <v>-69.17681</v>
-      </c>
-      <c r="I36" t="n">
-        <v>215</v>
-      </c>
-      <c r="J36" t="n">
-        <v>17</v>
-      </c>
-      <c r="K36" t="n">
-        <v>0</v>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>-12.597001</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>-69.17681</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>215</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
@@ -2341,20 +2679,30 @@
           <t>NIÑOS DE JESUS</t>
         </is>
       </c>
-      <c r="G37" t="n">
-        <v>-12.59801</v>
-      </c>
-      <c r="H37" t="n">
-        <v>-69.18612</v>
-      </c>
-      <c r="I37" t="n">
-        <v>247</v>
-      </c>
-      <c r="J37" t="n">
-        <v>20</v>
-      </c>
-      <c r="K37" t="n">
-        <v>0</v>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>-12.59801</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>-69.18612</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>247</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
@@ -2393,20 +2741,30 @@
           <t>52265 MARCELINO CHAMPAGNAT</t>
         </is>
       </c>
-      <c r="G38" t="n">
-        <v>-12.602519</v>
-      </c>
-      <c r="H38" t="n">
-        <v>-69.21020900000001</v>
-      </c>
-      <c r="I38" t="n">
-        <v>746</v>
-      </c>
-      <c r="J38" t="n">
-        <v>29</v>
-      </c>
-      <c r="K38" t="n">
-        <v>0</v>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>-12.602519</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>-69.210209</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>746</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
@@ -2445,20 +2803,30 @@
           <t>52267 MICAELA BASTIDAS</t>
         </is>
       </c>
-      <c r="G39" t="n">
-        <v>-12.622308</v>
-      </c>
-      <c r="H39" t="n">
-        <v>-69.21691199999999</v>
-      </c>
-      <c r="I39" t="n">
-        <v>243</v>
-      </c>
-      <c r="J39" t="n">
-        <v>9</v>
-      </c>
-      <c r="K39" t="n">
-        <v>0</v>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>-12.622308</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>-69.216912</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>243</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
@@ -2497,20 +2865,30 @@
           <t>SAN JUAN BAUTISTA DE LA SALLE</t>
         </is>
       </c>
-      <c r="G40" t="n">
-        <v>-12.59778</v>
-      </c>
-      <c r="H40" t="n">
-        <v>-69.18675</v>
-      </c>
-      <c r="I40" t="n">
-        <v>415</v>
-      </c>
-      <c r="J40" t="n">
-        <v>22</v>
-      </c>
-      <c r="K40" t="n">
-        <v>0</v>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>-12.59778</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>-69.18675</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>415</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
@@ -2549,20 +2927,30 @@
           <t>JARDIN TROPICAL</t>
         </is>
       </c>
-      <c r="G41" t="n">
-        <v>-12.5908</v>
-      </c>
-      <c r="H41" t="n">
-        <v>-69.1974</v>
-      </c>
-      <c r="I41" t="n">
-        <v>311</v>
-      </c>
-      <c r="J41" t="n">
-        <v>13</v>
-      </c>
-      <c r="K41" t="n">
-        <v>0</v>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>-12.5908</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>-69.1974</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>311</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>

--- a/ZonasEscolares/excels/MADRE_DE_DIOS-TAMBOPATA-TAMBOPATA.xlsx
+++ b/ZonasEscolares/excels/MADRE_DE_DIOS-TAMBOPATA-TAMBOPATA.xlsx
@@ -501,42 +501,42 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>393979</t>
+          <t>394097</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>261 NUESTRA SEÑORA DE LA ESPERANZA</t>
+          <t>310 RAYITOS DEL SOL</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-12.5839</t>
+          <t>-12.593892</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>-69.19143</t>
+          <t>-69.197019</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>342</t>
+          <t>250</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>10</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -563,32 +563,32 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>394016</t>
+          <t>394771</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>267 CORAZON DE MARIA</t>
+          <t>SANTA RITA DE CASIA</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-12.5921</t>
+          <t>-12.58893</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-69.1972</t>
+          <t>-69.19839</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>215</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -625,32 +625,32 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>394021</t>
+          <t>394059</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>52020 CAP. FAP JOSE ABELARDO QUIÑONES</t>
+          <t>296 LAS PALMERAS</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-12.602946</t>
+          <t>-12.59045</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-69.212059</t>
+          <t>-69.19264</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1147</t>
+          <t>311</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>12</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -687,37 +687,37 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>394040</t>
+          <t>393979</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>295 ARCO IRIS</t>
+          <t>261 NUESTRA SEÑORA DE LA ESPERANZA</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-12.6031</t>
+          <t>-12.5839</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-69.183</t>
+          <t>-69.19143</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>262</t>
+          <t>342</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>13</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -749,22 +749,22 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>394059</t>
+          <t>854268</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>296 LAS PALMERAS</t>
+          <t>JARDIN TROPICAL</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-12.59045</t>
+          <t>-12.5908</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-69.19264</t>
+          <t>-69.1974</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -774,7 +774,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -784,7 +784,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -811,32 +811,32 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>394064</t>
+          <t>394605</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>297</t>
+          <t>CARLOS FERMIN FITZCARRALD / COAR MADRE DE DIOS</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-12.59538</t>
+          <t>-12.591576</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-69.18209</t>
+          <t>-69.188401</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>587</t>
+          <t>2784</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>130</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>394097</t>
+          <t>553623</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>310 RAYITOS DEL SOL</t>
+          <t>MARIA MOLINARI REATEGUI</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-12.593892</t>
+          <t>-12.58061</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-69.197019</t>
+          <t>-69.1931</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>250</t>
+          <t>324</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>15</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -908,7 +908,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -935,37 +935,37 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>394120</t>
+          <t>756809</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>315 HUERTO INFANTIL</t>
+          <t>269 JARDIN DE DIOS</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-12.594395</t>
+          <t>-12.601576</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-69.192439</t>
+          <t>-69.212797</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>465</t>
+          <t>348</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -997,37 +997,37 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>394144</t>
+          <t>394120</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>318 MI PEQUEÑO MUNDO</t>
+          <t>315 HUERTO INFANTIL</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-12.6015</t>
+          <t>-12.594395</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-69.191</t>
+          <t>-69.192439</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>217</t>
+          <t>465</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>16</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1059,32 +1059,32 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>394177</t>
+          <t>394484</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>52001 SANTA ROSA</t>
+          <t>52166 NUESTRA SEÑORA DE FATIMA</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-12.587535</t>
+          <t>-12.6056</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-69.202779</t>
+          <t>-69.1899</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>832</t>
+          <t>431</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>17</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1121,32 +1121,32 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>394200</t>
+          <t>571778</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>NUESTRA SEÑORA DE LAS MERCEDES</t>
+          <t>TRILCE</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-12.592886</t>
+          <t>-12.59366</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-69.179865</t>
+          <t>-69.19552</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>1555</t>
+          <t>313</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>17</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1183,37 +1183,37 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>394238</t>
+          <t>756951</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>52008 SANTA CRUZ</t>
+          <t>MARIA REINA</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-12.59631</t>
+          <t>-12.597001</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>-69.18765</t>
+          <t>-69.17681</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>814</t>
+          <t>215</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>17</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -1245,32 +1245,32 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>394243</t>
+          <t>533753</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>LA PASTORA</t>
+          <t>CAP. ALIPIO PONCE VASQUEZ</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-12.585947</t>
+          <t>-12.601875</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-69.21302</t>
+          <t>-69.196872</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>1325</t>
+          <t>473</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>18</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -1307,37 +1307,37 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>394276</t>
+          <t>394573</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>DOS DE MAYO</t>
+          <t>52194 CAPITAN ALIPIO PONCE VASQUEZ</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>-12.58447</t>
+          <t>-12.60278</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-69.19069</t>
+          <t>-69.19305</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>2398</t>
+          <t>652</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>20</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -1369,32 +1369,32 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>394484</t>
+          <t>744901</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>52166 NUESTRA SEÑORA DE FATIMA</t>
+          <t>NUESTRA SEÑORA DE LA MERCED</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-12.6056</t>
+          <t>-12.58876</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-69.1899</t>
+          <t>-69.19971</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>431</t>
+          <t>304</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>20</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1431,32 +1431,32 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>394511</t>
+          <t>756970</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>52183</t>
+          <t>NIÑOS DE JESUS</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>-12.55695</t>
+          <t>-12.59801</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>-69.20533</t>
+          <t>-69.18612</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>461</t>
+          <t>247</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>20</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1493,32 +1493,32 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>394573</t>
+          <t>394511</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>52194 CAPITAN ALIPIO PONCE VASQUEZ</t>
+          <t>52183</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-12.60278</t>
+          <t>-12.55695</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-69.19305</t>
+          <t>-69.20533</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>652</t>
+          <t>461</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>21</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -1555,32 +1555,32 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>394587</t>
+          <t>394064</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>FAUSTINO MALDONADO</t>
+          <t>297</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>-12.59756</t>
+          <t>-12.59538</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>-69.17791</t>
+          <t>-69.18209</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>1656</t>
+          <t>587</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>22</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -1590,7 +1590,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1617,32 +1617,32 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>394592</t>
+          <t>828175</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>AUGUSTO BOURONCLE ACUÑA</t>
+          <t>SAN JUAN BAUTISTA DE LA SALLE</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>-12.5997</t>
+          <t>-12.59778</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>-69.1838</t>
+          <t>-69.18675</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1861</t>
+          <t>415</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>22</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -1679,32 +1679,32 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>394605</t>
+          <t>553637</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>CARLOS FERMIN FITZCARRALD / COAR MADRE DE DIOS</t>
+          <t>SANTA FE</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>-12.591576</t>
+          <t>-12.60276</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-69.188401</t>
+          <t>-69.19073</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>2784</t>
+          <t>444</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>130</t>
+          <t>24</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -1741,32 +1741,32 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>394610</t>
+          <t>394870</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>APLICACION NUESTRA SEÑORA DEL ROSARIO</t>
+          <t>52072 MARIO VARGAS LLOSA</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>-12.59046</t>
+          <t>-13.0761</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-69.19501</t>
+          <t>-70.3591</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>1346</t>
+          <t>552</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>25</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -1803,32 +1803,32 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>394629</t>
+          <t>394733</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>EMBLEMATICO GUILLERMO BILLINGHURST</t>
+          <t>SAN ISIDRO</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>-12.6005</t>
+          <t>-12.592248</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-69.1826</t>
+          <t>-69.186452</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>1294</t>
+          <t>260</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>26</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -1865,32 +1865,32 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>394728</t>
+          <t>827449</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>JAIME WHITE</t>
+          <t>52265 MARCELINO CHAMPAGNAT</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>-12.59808</t>
+          <t>-12.602519</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>-69.18971</t>
+          <t>-69.210209</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>885</t>
+          <t>746</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>29</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -1900,7 +1900,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1927,32 +1927,32 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>394733</t>
+          <t>395092</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>SAN ISIDRO</t>
+          <t>JORGE CHAVEZ RENGIFO</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>-12.592248</t>
+          <t>-12.279092</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>-69.186452</t>
+          <t>-69.148879</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>260</t>
+          <t>447</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>30</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -1989,37 +1989,37 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>394771</t>
+          <t>394238</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>SANTA RITA DE CASIA</t>
+          <t>52008 SANTA CRUZ</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>-12.58893</t>
+          <t>-12.59631</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>-69.19839</t>
+          <t>-69.18765</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>215</t>
+          <t>814</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>39</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
@@ -2051,32 +2051,32 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>394870</t>
+          <t>394728</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>52072 MARIO VARGAS LLOSA</t>
+          <t>JAIME WHITE</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>-13.0761</t>
+          <t>-12.59808</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>-70.3591</t>
+          <t>-69.18971</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>552</t>
+          <t>885</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>42</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -2086,7 +2086,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -2113,32 +2113,32 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>395092</t>
+          <t>394177</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>JORGE CHAVEZ RENGIFO</t>
+          <t>52001 SANTA ROSA</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>-12.279092</t>
+          <t>-12.587535</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>-69.148879</t>
+          <t>-69.202779</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>447</t>
+          <t>832</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>45</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -2175,32 +2175,32 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>511911</t>
+          <t>394021</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>361 SEÑOR DE LOS MILAGROS / 52181 SEÑOR DE LOS MILAGROS / SEÑOR DE LOS MILAGROS</t>
+          <t>52020 CAP. FAP JOSE ABELARDO QUIÑONES</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>-12.59528</t>
+          <t>-12.602946</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>-69.20014</t>
+          <t>-69.212059</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>1147</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>53</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -2210,7 +2210,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -2237,32 +2237,32 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>533753</t>
+          <t>394610</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>CAP. ALIPIO PONCE VASQUEZ</t>
+          <t>APLICACION NUESTRA SEÑORA DEL ROSARIO</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>-12.601875</t>
+          <t>-12.59046</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>-69.196872</t>
+          <t>-69.19501</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>473</t>
+          <t>1346</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>56</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -2272,7 +2272,7 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2299,32 +2299,32 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>553623</t>
+          <t>394243</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>MARIA MOLINARI REATEGUI</t>
+          <t>LA PASTORA</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>-12.58061</t>
+          <t>-12.585947</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>-69.1931</t>
+          <t>-69.21302</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>324</t>
+          <t>1325</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>60</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -2334,7 +2334,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -2361,32 +2361,32 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>553637</t>
+          <t>394200</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>SANTA FE</t>
+          <t>NUESTRA SEÑORA DE LAS MERCEDES</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>-12.60276</t>
+          <t>-12.592886</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>-69.19073</t>
+          <t>-69.179865</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>444</t>
+          <t>1555</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>63</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -2423,32 +2423,32 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>571778</t>
+          <t>394587</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>TRILCE</t>
+          <t>FAUSTINO MALDONADO</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>-12.59366</t>
+          <t>-12.59756</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>-69.19552</t>
+          <t>-69.17791</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>313</t>
+          <t>1656</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>64</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -2458,7 +2458,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -2485,32 +2485,32 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>744901</t>
+          <t>394629</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>NUESTRA SEÑORA DE LA MERCED</t>
+          <t>EMBLEMATICO GUILLERMO BILLINGHURST</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>-12.58876</t>
+          <t>-12.6005</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>-69.19971</t>
+          <t>-69.1826</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>304</t>
+          <t>1294</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>65</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
@@ -2520,7 +2520,7 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2547,32 +2547,32 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>756809</t>
+          <t>394592</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>269 JARDIN DE DIOS</t>
+          <t>AUGUSTO BOURONCLE ACUÑA</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>-12.601576</t>
+          <t>-12.5997</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>-69.212797</t>
+          <t>-69.1838</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>348</t>
+          <t>1861</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>67</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
@@ -2609,32 +2609,32 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>756951</t>
+          <t>394144</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>MARIA REINA</t>
+          <t>318 MI PEQUEÑO MUNDO</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>-12.597001</t>
+          <t>-12.6015</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>-69.17681</t>
+          <t>-69.191</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>215</t>
+          <t>217</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>8</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
@@ -2671,32 +2671,32 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>756970</t>
+          <t>511911</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>NIÑOS DE JESUS</t>
+          <t>361 SEÑOR DE LOS MILAGROS / 52181 SEÑOR DE LOS MILAGROS / SEÑOR DE LOS MILAGROS</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>-12.59801</t>
+          <t>-12.59528</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>-69.18612</t>
+          <t>-69.20014</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>247</t>
+          <t>2030</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>82</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
@@ -2706,7 +2706,7 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2733,32 +2733,32 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>827449</t>
+          <t>394016</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>52265 MARCELINO CHAMPAGNAT</t>
+          <t>267 CORAZON DE MARIA</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>-12.602519</t>
+          <t>-12.5921</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>-69.210209</t>
+          <t>-69.1972</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>746</t>
+          <t>200</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>9</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
@@ -2795,27 +2795,27 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>827454</t>
+          <t>394040</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>52267 MICAELA BASTIDAS</t>
+          <t>295 ARCO IRIS</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>-12.622308</t>
+          <t>-12.6031</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>-69.216912</t>
+          <t>-69.183</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>243</t>
+          <t>262</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -2857,32 +2857,32 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>828175</t>
+          <t>827454</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>SAN JUAN BAUTISTA DE LA SALLE</t>
+          <t>52267 MICAELA BASTIDAS</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>-12.59778</t>
+          <t>-12.622308</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>-69.18675</t>
+          <t>-69.216912</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>415</t>
+          <t>243</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>9</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
@@ -2919,37 +2919,37 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>854268</t>
+          <t>394276</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>JARDIN TROPICAL</t>
+          <t>DOS DE MAYO</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>-12.5908</t>
+          <t>-12.58447</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>-69.1974</t>
+          <t>-69.19069</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>311</t>
+          <t>2398</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>92</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">

--- a/ZonasEscolares/excels/MADRE_DE_DIOS-TAMBOPATA-TAMBOPATA.xlsx
+++ b/ZonasEscolares/excels/MADRE_DE_DIOS-TAMBOPATA-TAMBOPATA.xlsx
@@ -501,32 +501,32 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>394097</t>
+          <t>854268</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>310 RAYITOS DEL SOL</t>
+          <t>JARDIN TROPICAL</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-12.593892</t>
+          <t>311</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>-69.197019</t>
+          <t>13</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>250</t>
+          <t>-12.5908</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>-69.1974</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -536,7 +536,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -563,32 +563,32 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>394771</t>
+          <t>828175</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>SANTA RITA DE CASIA</t>
+          <t>SAN JUAN BAUTISTA DE LA SALLE</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-12.58893</t>
+          <t>415</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-69.19839</t>
+          <t>22</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>215</t>
+          <t>-12.59778</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>-69.18675</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -625,32 +625,32 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>394059</t>
+          <t>827454</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>296 LAS PALMERAS</t>
+          <t>52267 MICAELA BASTIDAS</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-12.59045</t>
+          <t>243</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-69.19264</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>311</t>
+          <t>-12.622308</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>-69.216912</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -660,7 +660,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -687,37 +687,37 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>393979</t>
+          <t>827449</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>261 NUESTRA SEÑORA DE LA ESPERANZA</t>
+          <t>52265 MARCELINO CHAMPAGNAT</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-12.5839</t>
+          <t>746</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-69.19143</t>
+          <t>29</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>342</t>
+          <t>-12.602519</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>-69.210209</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -749,32 +749,32 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>854268</t>
+          <t>756970</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>JARDIN TROPICAL</t>
+          <t>NIÑOS DE JESUS</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-12.5908</t>
+          <t>247</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-69.1974</t>
+          <t>20</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>311</t>
+          <t>-12.59801</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>-69.18612</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -784,7 +784,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -811,32 +811,32 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>394605</t>
+          <t>756951</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>CARLOS FERMIN FITZCARRALD / COAR MADRE DE DIOS</t>
+          <t>MARIA REINA</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-12.591576</t>
+          <t>215</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-69.188401</t>
+          <t>17</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>2784</t>
+          <t>-12.597001</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>130</t>
+          <t>-69.17681</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>553623</t>
+          <t>756809</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>MARIA MOLINARI REATEGUI</t>
+          <t>269 JARDIN DE DIOS</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-12.58061</t>
+          <t>348</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-69.1931</t>
+          <t>15</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>324</t>
+          <t>-12.601576</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>-69.212797</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -935,32 +935,32 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>756809</t>
+          <t>744901</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>269 JARDIN DE DIOS</t>
+          <t>NUESTRA SEÑORA DE LA MERCED</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-12.601576</t>
+          <t>304</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-69.212797</t>
+          <t>20</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>348</t>
+          <t>-12.58876</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>-69.19971</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -970,7 +970,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -997,37 +997,37 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>394120</t>
+          <t>571778</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>315 HUERTO INFANTIL</t>
+          <t>TRILCE</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-12.594395</t>
+          <t>313</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-69.192439</t>
+          <t>17</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>465</t>
+          <t>-12.59366</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>-69.19552</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1059,32 +1059,32 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>394484</t>
+          <t>553637</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>52166 NUESTRA SEÑORA DE FATIMA</t>
+          <t>SANTA FE</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-12.6056</t>
+          <t>444</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-69.1899</t>
+          <t>24</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>431</t>
+          <t>-12.60276</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>-69.19073</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1121,32 +1121,32 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>571778</t>
+          <t>553623</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>TRILCE</t>
+          <t>MARIA MOLINARI REATEGUI</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-12.59366</t>
+          <t>324</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-69.19552</t>
+          <t>15</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>313</t>
+          <t>-12.58061</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>-69.1931</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1183,32 +1183,32 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>756951</t>
+          <t>533753</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>MARIA REINA</t>
+          <t>CAP. ALIPIO PONCE VASQUEZ</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-12.597001</t>
+          <t>473</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>-69.17681</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>215</t>
+          <t>-12.601875</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>-69.196872</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1245,32 +1245,32 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>533753</t>
+          <t>511911</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>CAP. ALIPIO PONCE VASQUEZ</t>
+          <t>361 SEÑOR DE LOS MILAGROS / 52181 SEÑOR DE LOS MILAGROS / SEÑOR DE LOS MILAGROS</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-12.601875</t>
+          <t>2030</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-69.196872</t>
+          <t>82</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>473</t>
+          <t>-12.59528</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>-69.20014</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -1280,7 +1280,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1307,32 +1307,32 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>394573</t>
+          <t>395092</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>52194 CAPITAN ALIPIO PONCE VASQUEZ</t>
+          <t>JORGE CHAVEZ RENGIFO</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>-12.60278</t>
+          <t>447</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-69.19305</t>
+          <t>30</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>652</t>
+          <t>-12.279092</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>-69.148879</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -1369,32 +1369,32 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>744901</t>
+          <t>394870</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>NUESTRA SEÑORA DE LA MERCED</t>
+          <t>52072 MARIO VARGAS LLOSA</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-12.58876</t>
+          <t>552</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-69.19971</t>
+          <t>25</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>304</t>
+          <t>-13.0761</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>-70.3591</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1431,32 +1431,32 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>756970</t>
+          <t>394771</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>NIÑOS DE JESUS</t>
+          <t>SANTA RITA DE CASIA</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>-12.59801</t>
+          <t>215</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>-69.18612</t>
+          <t>10</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>247</t>
+          <t>-12.58893</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>-69.19839</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1493,32 +1493,32 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>394511</t>
+          <t>394733</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>52183</t>
+          <t>SAN ISIDRO</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-12.55695</t>
+          <t>260</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-69.20533</t>
+          <t>26</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>461</t>
+          <t>-12.592248</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>-69.186452</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -1555,32 +1555,32 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>394064</t>
+          <t>394728</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>297</t>
+          <t>JAIME WHITE</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>-12.59538</t>
+          <t>885</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>-69.18209</t>
+          <t>42</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>587</t>
+          <t>-12.59808</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>-69.18971</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -1590,7 +1590,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1617,32 +1617,32 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>828175</t>
+          <t>394629</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>SAN JUAN BAUTISTA DE LA SALLE</t>
+          <t>EMBLEMATICO GUILLERMO BILLINGHURST</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>-12.59778</t>
+          <t>1294</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>-69.18675</t>
+          <t>65</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>415</t>
+          <t>-12.6005</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>-69.1826</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -1679,32 +1679,32 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>553637</t>
+          <t>394610</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>SANTA FE</t>
+          <t>APLICACION NUESTRA SEÑORA DEL ROSARIO</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>-12.60276</t>
+          <t>1346</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-69.19073</t>
+          <t>56</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>444</t>
+          <t>-12.59046</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>-69.19501</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -1741,32 +1741,32 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>394870</t>
+          <t>394605</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>52072 MARIO VARGAS LLOSA</t>
+          <t>CARLOS FERMIN FITZCARRALD / COAR MADRE DE DIOS</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>-13.0761</t>
+          <t>2784</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-70.3591</t>
+          <t>130</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>552</t>
+          <t>-12.591576</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>-69.188401</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -1803,32 +1803,32 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>394733</t>
+          <t>394592</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>SAN ISIDRO</t>
+          <t>AUGUSTO BOURONCLE ACUÑA</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>-12.592248</t>
+          <t>1861</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-69.186452</t>
+          <t>67</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>260</t>
+          <t>-12.5997</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>-69.1838</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -1865,32 +1865,32 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>827449</t>
+          <t>394587</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>52265 MARCELINO CHAMPAGNAT</t>
+          <t>FAUSTINO MALDONADO</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>-12.602519</t>
+          <t>1656</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>-69.210209</t>
+          <t>64</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>746</t>
+          <t>-12.59756</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>-69.17791</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -1900,7 +1900,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1927,32 +1927,32 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>395092</t>
+          <t>394573</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>JORGE CHAVEZ RENGIFO</t>
+          <t>52194 CAPITAN ALIPIO PONCE VASQUEZ</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>-12.279092</t>
+          <t>652</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>-69.148879</t>
+          <t>20</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>447</t>
+          <t>-12.60278</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>-69.19305</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -1989,37 +1989,37 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>394238</t>
+          <t>394511</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>52008 SANTA CRUZ</t>
+          <t>52183</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>-12.59631</t>
+          <t>461</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>-69.18765</t>
+          <t>21</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>814</t>
+          <t>-12.55695</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>-69.20533</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
@@ -2051,32 +2051,32 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>394728</t>
+          <t>394484</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>JAIME WHITE</t>
+          <t>52166 NUESTRA SEÑORA DE FATIMA</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>-12.59808</t>
+          <t>431</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>-69.18971</t>
+          <t>17</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>885</t>
+          <t>-12.6056</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>-69.1899</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -2086,7 +2086,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2113,37 +2113,37 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>394177</t>
+          <t>394276</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>52001 SANTA ROSA</t>
+          <t>DOS DE MAYO</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>-12.587535</t>
+          <t>2398</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>-69.202779</t>
+          <t>92</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>832</t>
+          <t>-12.58447</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>-69.19069</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
@@ -2175,32 +2175,32 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>394021</t>
+          <t>394243</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>52020 CAP. FAP JOSE ABELARDO QUIÑONES</t>
+          <t>LA PASTORA</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>-12.602946</t>
+          <t>1325</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>-69.212059</t>
+          <t>60</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>1147</t>
+          <t>-12.585947</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>-69.21302</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -2237,37 +2237,37 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>394610</t>
+          <t>394238</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>APLICACION NUESTRA SEÑORA DEL ROSARIO</t>
+          <t>52008 SANTA CRUZ</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>-12.59046</t>
+          <t>814</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>-69.19501</t>
+          <t>39</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>1346</t>
+          <t>-12.59631</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>-69.18765</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
@@ -2299,32 +2299,32 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>394243</t>
+          <t>394200</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>LA PASTORA</t>
+          <t>NUESTRA SEÑORA DE LAS MERCEDES</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>-12.585947</t>
+          <t>1555</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>-69.21302</t>
+          <t>63</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>1325</t>
+          <t>-12.592886</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>-69.179865</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -2334,7 +2334,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2361,32 +2361,32 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>394200</t>
+          <t>394177</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>NUESTRA SEÑORA DE LAS MERCEDES</t>
+          <t>52001 SANTA ROSA</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>-12.592886</t>
+          <t>832</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>-69.179865</t>
+          <t>45</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>1555</t>
+          <t>-12.587535</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>-69.202779</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -2423,32 +2423,32 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>394587</t>
+          <t>394144</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>FAUSTINO MALDONADO</t>
+          <t>318 MI PEQUEÑO MUNDO</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>-12.59756</t>
+          <t>217</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>-69.17791</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>1656</t>
+          <t>-12.6015</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>-69.191</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -2458,7 +2458,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2485,37 +2485,37 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>394629</t>
+          <t>394120</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>EMBLEMATICO GUILLERMO BILLINGHURST</t>
+          <t>315 HUERTO INFANTIL</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>-12.6005</t>
+          <t>465</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>-69.1826</t>
+          <t>16</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>1294</t>
+          <t>-12.594395</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>-69.192439</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
@@ -2547,32 +2547,32 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>394592</t>
+          <t>394097</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>AUGUSTO BOURONCLE ACUÑA</t>
+          <t>310 RAYITOS DEL SOL</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>-12.5997</t>
+          <t>250</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>-69.1838</t>
+          <t>10</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>1861</t>
+          <t>-12.593892</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>-69.197019</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
@@ -2582,7 +2582,7 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -2609,32 +2609,32 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>394144</t>
+          <t>394064</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>318 MI PEQUEÑO MUNDO</t>
+          <t>297</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>-12.6015</t>
+          <t>587</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>-69.191</t>
+          <t>22</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>217</t>
+          <t>-12.59538</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>-69.18209</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
@@ -2671,32 +2671,32 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>511911</t>
+          <t>394059</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>361 SEÑOR DE LOS MILAGROS / 52181 SEÑOR DE LOS MILAGROS / SEÑOR DE LOS MILAGROS</t>
+          <t>296 LAS PALMERAS</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>-12.59528</t>
+          <t>311</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>-69.20014</t>
+          <t>12</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>-12.59045</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>-69.19264</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
@@ -2706,7 +2706,7 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -2733,32 +2733,32 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>394016</t>
+          <t>394040</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>267 CORAZON DE MARIA</t>
+          <t>295 ARCO IRIS</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>-12.5921</t>
+          <t>262</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>-69.1972</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>-12.6031</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>-69.183</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
@@ -2795,32 +2795,32 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>394040</t>
+          <t>394021</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>295 ARCO IRIS</t>
+          <t>52020 CAP. FAP JOSE ABELARDO QUIÑONES</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>-12.6031</t>
+          <t>1147</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>-69.183</t>
+          <t>53</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>262</t>
+          <t>-12.602946</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>-69.212059</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
@@ -2830,7 +2830,7 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -2857,32 +2857,32 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>827454</t>
+          <t>394016</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>52267 MICAELA BASTIDAS</t>
+          <t>267 CORAZON DE MARIA</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>-12.622308</t>
+          <t>200</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>-69.216912</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>243</t>
+          <t>-12.5921</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>-69.1972</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
@@ -2919,32 +2919,32 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>394276</t>
+          <t>393979</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>DOS DE MAYO</t>
+          <t>261 NUESTRA SEÑORA DE LA ESPERANZA</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>-12.58447</t>
+          <t>342</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>-69.19069</t>
+          <t>13</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>2398</t>
+          <t>-12.5839</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>-69.19143</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">

--- a/ZonasEscolares/excels/MADRE_DE_DIOS-TAMBOPATA-TAMBOPATA.xlsx
+++ b/ZonasEscolares/excels/MADRE_DE_DIOS-TAMBOPATA-TAMBOPATA.xlsx
@@ -449,22 +449,22 @@
       </c>
       <c r="G1" t="inlineStr">
         <is>
+          <t>alumnos</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>docentes</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
           <t>latitud</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>longitud</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>alumnos</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>docentes</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
